--- a/tams-common-basicdata/src/main/resources/tpl/ComInterestRateQuotationInfo001.xlsx
+++ b/tams-common-basicdata/src/main/resources/tpl/ComInterestRateQuotationInfo001.xlsx
@@ -12,12 +12,11 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>发布日</t>
   </si>
@@ -33,6 +32,96 @@
   <si>
     <t>利率值%</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNY:人民币（cny）</t>
+  </si>
+  <si>
+    <t>HKD:港元（hkd）</t>
+  </si>
+  <si>
+    <t>USD:美元（usd）</t>
+  </si>
+  <si>
+    <t>EUR:欧元（eur）</t>
+  </si>
+  <si>
+    <t>JPY:日元（jpy）</t>
+  </si>
+  <si>
+    <t>MOP:澳门元（mop）</t>
+  </si>
+  <si>
+    <t>CHF:瑞士法郎（chf）</t>
+  </si>
+  <si>
+    <t>GBP:英镑（gbp）</t>
+  </si>
+  <si>
+    <t>RUB:俄罗斯卢布（rub）</t>
+  </si>
+  <si>
+    <t>CAD:加拿大元（cad）</t>
+  </si>
+  <si>
+    <t>DKK:丹麦克朗（dkk）</t>
+  </si>
+  <si>
+    <t>AUD:澳大利亚元（aud）</t>
+  </si>
+  <si>
+    <t>SEK:瑞典克朗（sek）</t>
+  </si>
+  <si>
+    <t>SGD:新加坡元（sgd）</t>
+  </si>
+  <si>
+    <t>TWD:新台币（twd）</t>
+  </si>
+  <si>
+    <t>AED:阿联酋迪拉姆(aed)</t>
+  </si>
+  <si>
+    <t>HUF:匈牙利福林(huf)</t>
+  </si>
+  <si>
+    <t>KHR:柬埔寨瑞尔(khr)</t>
+  </si>
+  <si>
+    <t>KRW:韩元(krw)</t>
+  </si>
+  <si>
+    <t>KZT:哈萨克斯坦坚戈(kzt)</t>
+  </si>
+  <si>
+    <t>MNT:蒙古图格里克 (mnt)</t>
+  </si>
+  <si>
+    <t>MXN:墨西哥元(mxn)</t>
+  </si>
+  <si>
+    <t>MYR:马来西亚林吉特(myr)</t>
+  </si>
+  <si>
+    <t>NOK:挪威克朗(nok)</t>
+  </si>
+  <si>
+    <t>NZD:新西兰元(nzd)</t>
+  </si>
+  <si>
+    <t>PLN:波兰兹罗提(pln)</t>
+  </si>
+  <si>
+    <t>SAR:沙特里亚尔(sar)</t>
+  </si>
+  <si>
+    <t>THB:泰铢(thb)</t>
+  </si>
+  <si>
+    <t>TRY:新土耳其里拉(try)</t>
+  </si>
+  <si>
+    <t>ZAR:南非兰特(zar)</t>
   </si>
 </sst>
 </file>
@@ -75,8 +164,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -382,9 +474,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="22" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -404,14 +499,185 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>Sheet2!$A$2:$A$31</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
+  <dimension ref="A1:A31"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.08984375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -420,7 +686,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
